--- a/dataset_t6_grouped/results2/G0/G0_DMSO_W0082F0002T0006Z000C1N87_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G0/G0_DMSO_W0082F0002T0006Z000C1N87_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>36.84726340798269</v>
+        <v>5.987680303797188</v>
       </c>
       <c r="D2" t="n">
-        <v>38.67661506831436</v>
+        <v>6.284949948601084</v>
       </c>
       <c r="E2" t="n">
-        <v>4.976277148777243</v>
+        <v>0.8086450366763022</v>
       </c>
       <c r="F2" t="n">
-        <v>4.61694118093021</v>
+        <v>0.7502529419011592</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>34.59785629449176</v>
+        <v>5.622151647854911</v>
       </c>
       <c r="D3" t="n">
-        <v>34.02178038765832</v>
+        <v>5.528539312994478</v>
       </c>
       <c r="E3" t="n">
-        <v>4.976277148777243</v>
+        <v>0.8086450366763022</v>
       </c>
       <c r="F3" t="n">
-        <v>4.61694118093021</v>
+        <v>0.7502529419011592</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>25.34758371127315</v>
+        <v>4.118982353081887</v>
       </c>
       <c r="D4" t="n">
-        <v>27.42327805668171</v>
+        <v>4.456282684210779</v>
       </c>
       <c r="E4" t="n">
-        <v>4.976277148777243</v>
+        <v>0.8086450366763022</v>
       </c>
       <c r="F4" t="n">
-        <v>4.61694118093021</v>
+        <v>0.7502529419011592</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
